--- a/samples/Sample_7_For_School_Management_Section_A_Class7.xlsx
+++ b/samples/Sample_7_For_School_Management_Section_A_Class7.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Devansh Gowda</t>
+          <t>Aditya Desai</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Swathi Hegde</t>
+          <t>Tanya Naik</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Reyansh Kulkarni</t>
+          <t>Karthik Hegde</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Neha Murthy</t>
+          <t>Myra Verma</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sameer Naik</t>
+          <t>Yash Reddy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Aadhya Joshi</t>
+          <t>Riya Hegde</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reyansh Gowda</t>
+          <t>Varun Nair</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tanya Prabhu</t>
+          <t>Sara Kumar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohan Prabhu</t>
+          <t>Rahul Rao</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Divya Shetty</t>
+          <t>Kritika Shetty</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ishaan Nair</t>
+          <t>Nikhil Verma</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ishita Murthy</t>
+          <t>Diya Sharma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vivaan Desai</t>
+          <t>Rahul Patel</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Divya Pai</t>
+          <t>Tanya Prabhu</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arjun Desai</t>
+          <t>Rohan Murthy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Priya Rao</t>
+          <t>Sara Naik</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ishaan Verma</t>
+          <t>Aarav Pai</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Shreya Desai</t>
+          <t>Kavya Singh</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Akash Iyer</t>
+          <t>Rohan Bhat</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kritika Gowda</t>
+          <t>Ananya Reddy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Arjun Naik</t>
+          <t>Aditya Rao</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Swathi Nair</t>
+          <t>Kavya Sharma</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pranav Joshi</t>
+          <t>Pranav Desai</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Diya Hegde</t>
+          <t>Diya Naik</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vikram Shetty</t>
+          <t>Pranav Sharma</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Priya Kulkarni</t>
+          <t>Myra Hegde</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reyansh Prabhu</t>
+          <t>Akash Hegde</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pooja Singh</t>
+          <t>Sneha Pai</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Arjun Bhat</t>
+          <t>Reyansh Sharma</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Kavya Gowda</t>
+          <t>Ananya Gowda</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1615,26 +1615,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
+          <t>Fractions &amp; Decimals</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -1646,29 +1646,29 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C3" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3" t="n">
         <v>41</v>
       </c>
-      <c r="D3" t="n">
-        <v>40</v>
-      </c>
       <c r="E3" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fractions &amp; Decimals</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1677,29 +1677,33 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Fractions &amp; Decimals</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Simple Equations</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1708,19 +1712,19 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" t="n">
+        <v>34</v>
+      </c>
+      <c r="D5" t="n">
         <v>32</v>
       </c>
-      <c r="C5" t="n">
-        <v>32</v>
-      </c>
-      <c r="D5" t="n">
-        <v>29</v>
-      </c>
       <c r="E5" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -1735,26 +1739,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Perimeter &amp; Area</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1770,16 +1774,16 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
         <v>9</v>
       </c>
-      <c r="C7" t="n">
-        <v>6</v>
-      </c>
-      <c r="D7" t="n">
-        <v>10</v>
-      </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F7" t="n">
         <v>10</v>
@@ -1792,7 +1796,11 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Needs urgent academic support, at risk of failing.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1801,29 +1809,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D8" t="n">
+        <v>15</v>
+      </c>
+      <c r="E8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
-        <v>17</v>
-      </c>
       <c r="F8" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Encouraging progress, on the right track now.</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1832,16 +1840,16 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C9" t="n">
+        <v>34</v>
+      </c>
+      <c r="D9" t="n">
         <v>30</v>
       </c>
-      <c r="C9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" t="n">
-        <v>32</v>
-      </c>
       <c r="E9" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="F9" t="n">
         <v>30</v>
@@ -1849,14 +1857,10 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -1867,24 +1871,28 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>38</v>
+      </c>
+      <c r="C10" t="n">
         <v>42</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>43</v>
       </c>
-      <c r="D10" t="n">
-        <v>41</v>
-      </c>
       <c r="E10" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -1894,26 +1902,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>19</v>
       </c>
       <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
         <v>18</v>
       </c>
-      <c r="E11" t="n">
-        <v>15</v>
-      </c>
-      <c r="F11" t="n">
-        <v>16</v>
-      </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Perimeter &amp; Area</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1925,24 +1933,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D12" t="n">
+        <v>45</v>
+      </c>
+      <c r="E12" t="n">
         <v>47</v>
       </c>
-      <c r="E12" t="n">
-        <v>50</v>
-      </c>
       <c r="F12" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Simple Equations</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
@@ -1952,24 +1964,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>42</v>
       </c>
-      <c r="D13" t="n">
-        <v>44</v>
-      </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -1979,29 +1995,33 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C14" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E14" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Average performance — revision of basics recommended.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2010,7 +2030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" t="n">
         <v>33</v>
@@ -2019,20 +2039,24 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F15" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Simple Equations</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2041,29 +2065,29 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D16" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" t="n">
+        <v>22</v>
+      </c>
+      <c r="F16" t="n">
         <v>21</v>
       </c>
-      <c r="E16" t="n">
-        <v>20</v>
-      </c>
-      <c r="F16" t="n">
-        <v>22</v>
-      </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2075,25 +2099,21 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
         <v>12</v>
       </c>
-      <c r="D17" t="n">
-        <v>16</v>
-      </c>
-      <c r="E17" t="n">
-        <v>11</v>
-      </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -2103,22 +2123,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2134,29 +2154,33 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>Simple Equations</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>On track, but should aim higher with focused practice.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2165,25 +2189,33 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>46</v>
+      </c>
+      <c r="C20" t="n">
+        <v>44</v>
+      </c>
+      <c r="D20" t="n">
+        <v>41</v>
+      </c>
+      <c r="E20" t="n">
         <v>43</v>
       </c>
-      <c r="C20" t="n">
-        <v>41</v>
-      </c>
-      <c r="D20" t="n">
-        <v>40</v>
-      </c>
-      <c r="E20" t="n">
-        <v>44</v>
-      </c>
       <c r="F20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2192,26 +2224,26 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="D21" t="n">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="F21" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Simple Equations</t>
+          <t>Ratio &amp; Proportion</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2223,26 +2255,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D22" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="E22" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
+          <t>Simple Equations</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2254,19 +2286,19 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D23" t="n">
         <v>44</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="F23" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -2285,19 +2317,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E24" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F24" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -2305,7 +2337,7 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -2316,28 +2348,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E25" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
@@ -2347,28 +2375,24 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
         <v>17</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
+        <v>18</v>
+      </c>
+      <c r="E26" t="n">
         <v>20</v>
       </c>
-      <c r="D26" t="n">
-        <v>14</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>17</v>
       </c>
-      <c r="F26" t="n">
-        <v>15</v>
-      </c>
       <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Perimeter &amp; Area</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -2381,17 +2405,17 @@
         <v>9</v>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" t="n">
         <v>7</v>
       </c>
-      <c r="F27" t="n">
-        <v>9</v>
-      </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
@@ -2400,7 +2424,11 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Needs urgent academic support, at risk of failing.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2409,24 +2437,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E28" t="n">
         <v>15</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Simple Equations</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>Encouraging progress, on the right track now.</t>
@@ -2443,30 +2475,26 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D29" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F29" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Steady but needs more consistency across topics.</t>
-        </is>
-      </c>
+          <t>Perimeter &amp; Area</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2475,7 +2503,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" t="n">
         <v>41</v>
@@ -2484,7 +2512,7 @@
         <v>39</v>
       </c>
       <c r="E30" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F30" t="n">
         <v>42</v>
@@ -2494,14 +2522,10 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Lines &amp; Angles</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Strong performer, small gains possible with more practice.</t>
-        </is>
-      </c>
+          <t>Fractions &amp; Decimals</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2510,33 +2534,29 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C31" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="D31" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E31" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Ratio &amp; Proportion</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ups and downs need to be understood — talk to student directly.</t>
-        </is>
-      </c>
+          <t>Lines &amp; Angles</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2617,28 +2637,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D2" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F2" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -2648,26 +2664,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C3" t="n">
         <v>79</v>
       </c>
       <c r="D3" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="E3" t="n">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F3" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -2679,26 +2695,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4" t="n">
         <v>59</v>
       </c>
       <c r="D4" t="n">
+        <v>55</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62</v>
+      </c>
+      <c r="F4" t="n">
         <v>60</v>
       </c>
-      <c r="E4" t="n">
-        <v>58</v>
-      </c>
-      <c r="F4" t="n">
-        <v>67</v>
-      </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -2710,33 +2726,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D5" t="n">
         <v>66</v>
       </c>
-      <c r="D5" t="n">
-        <v>61</v>
-      </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F5" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2745,24 +2753,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D6" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="E6" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
@@ -2772,26 +2784,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
         <v>17</v>
       </c>
       <c r="E7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Weather &amp; Climate</t>
+          <t>Motion &amp; Time</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -2803,33 +2815,29 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C8" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D8" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
-        </is>
-      </c>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2838,26 +2846,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C9" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D9" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="n">
+        <v>63</v>
+      </c>
+      <c r="F9" t="n">
         <v>59</v>
       </c>
-      <c r="F9" t="n">
-        <v>68</v>
-      </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -2869,16 +2877,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E10" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F10" t="n">
         <v>84</v>
@@ -2886,12 +2894,12 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2903,30 +2911,22 @@
         <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D11" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F11" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2941,13 +2941,13 @@
         <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E12" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -2957,11 +2957,7 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Exceptional performance, keep up this standard.</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2970,33 +2966,25 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E13" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F13" t="n">
         <v>86</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Motion &amp; Time</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3005,26 +2993,26 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="F14" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -3036,33 +3024,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E15" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>On track, but should aim higher with focused practice.</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3071,28 +3051,24 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>40</v>
+      </c>
+      <c r="C16" t="n">
+        <v>45</v>
+      </c>
+      <c r="D16" t="n">
         <v>37</v>
       </c>
-      <c r="C16" t="n">
-        <v>35</v>
-      </c>
-      <c r="D16" t="n">
-        <v>36</v>
-      </c>
       <c r="E16" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F16" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Weather &amp; Climate</t>
-        </is>
-      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -3102,33 +3078,29 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
+        <v>24</v>
+      </c>
+      <c r="E17" t="n">
+        <v>24</v>
+      </c>
+      <c r="F17" t="n">
         <v>25</v>
       </c>
-      <c r="E17" t="n">
-        <v>19</v>
-      </c>
-      <c r="F17" t="n">
-        <v>16</v>
-      </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Heat</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
-        </is>
-      </c>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3137,33 +3109,29 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="D18" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="E18" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F18" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
-        </is>
-      </c>
+          <t>Acids Bases &amp; Salts</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3172,28 +3140,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C19" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E19" t="n">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -3203,26 +3167,26 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="D20" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E20" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
+          <t>Nutrition in Plants</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -3234,28 +3198,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C21" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D21" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="E21" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F21" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
@@ -3265,26 +3225,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C22" t="n">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="D22" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="E22" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F22" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3296,29 +3256,33 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C23" t="n">
         <v>89</v>
       </c>
       <c r="D23" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E23" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="F23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Nutrition in Plants</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Strong performer, small gains possible with more practice.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3327,19 +3291,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="C24" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="D24" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="E24" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F24" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -3362,33 +3326,29 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="D25" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E25" t="n">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Acids Bases &amp; Salts</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Average performance — revision of basics recommended.</t>
-        </is>
-      </c>
+          <t>Motion &amp; Time</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3397,24 +3357,28 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>39</v>
+      </c>
+      <c r="C26" t="n">
+        <v>32</v>
+      </c>
+      <c r="D26" t="n">
         <v>37</v>
       </c>
-      <c r="C26" t="n">
-        <v>31</v>
-      </c>
-      <c r="D26" t="n">
-        <v>35</v>
-      </c>
       <c r="E26" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F26" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Weather &amp; Climate</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
@@ -3424,29 +3388,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D27" t="n">
         <v>16</v>
       </c>
-      <c r="D27" t="n">
-        <v>22</v>
-      </c>
       <c r="E27" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3455,24 +3415,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C28" t="n">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="D28" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="E28" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F28" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Nutrition in Plants</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
@@ -3482,26 +3446,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C29" t="n">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="D29" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E29" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Motion &amp; Time</t>
+          <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3513,19 +3477,19 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C30" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="D30" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="E30" t="n">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="F30" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -3544,26 +3508,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C31" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D31" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E31" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F31" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Heat</t>
+          <t>Weather &amp; Climate</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,26 +3611,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C2" t="n">
+        <v>46</v>
+      </c>
+      <c r="D2" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F2" t="n">
         <v>43</v>
       </c>
-      <c r="D2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E2" t="n">
-        <v>42</v>
-      </c>
-      <c r="F2" t="n">
-        <v>44</v>
-      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -3681,21 +3645,25 @@
         <v>41</v>
       </c>
       <c r="C3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" t="n">
         <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
@@ -3708,16 +3676,16 @@
         <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" t="n">
         <v>30</v>
       </c>
       <c r="F4" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3739,28 +3707,28 @@
         <v>35</v>
       </c>
       <c r="C5" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -3771,16 +3739,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D6" t="n">
+        <v>19</v>
+      </c>
+      <c r="E6" t="n">
         <v>21</v>
-      </c>
-      <c r="E6" t="n">
-        <v>19</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
@@ -3808,23 +3776,27 @@
         <v>10</v>
       </c>
       <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" t="n">
         <v>11</v>
       </c>
-      <c r="E7" t="n">
-        <v>9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8</v>
-      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Serious concern — immediate intervention needed.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3833,26 +3805,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
+        <v>34</v>
+      </c>
+      <c r="D8" t="n">
+        <v>37</v>
+      </c>
+      <c r="E8" t="n">
+        <v>33</v>
+      </c>
+      <c r="F8" t="n">
         <v>35</v>
       </c>
-      <c r="D8" t="n">
-        <v>32</v>
-      </c>
-      <c r="E8" t="n">
-        <v>30</v>
-      </c>
-      <c r="F8" t="n">
-        <v>34</v>
-      </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -3864,29 +3836,29 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3895,24 +3867,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>39</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E10" t="n">
         <v>41</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
@@ -3922,16 +3898,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F11" t="n">
         <v>37</v>
@@ -3939,12 +3915,12 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3953,26 +3929,26 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C12" t="n">
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Grammar - Tenses</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -3984,24 +3960,28 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E13" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F13" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
@@ -4011,24 +3991,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D14" t="n">
         <v>33</v>
       </c>
       <c r="E14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
@@ -4038,25 +4022,33 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>30</v>
+      </c>
+      <c r="C15" t="n">
+        <v>30</v>
+      </c>
+      <c r="D15" t="n">
+        <v>28</v>
+      </c>
+      <c r="E15" t="n">
+        <v>33</v>
+      </c>
+      <c r="F15" t="n">
         <v>31</v>
       </c>
-      <c r="C15" t="n">
-        <v>33</v>
-      </c>
-      <c r="D15" t="n">
-        <v>34</v>
-      </c>
-      <c r="E15" t="n">
-        <v>31</v>
-      </c>
-      <c r="F15" t="n">
-        <v>29</v>
-      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Steady but needs more consistency across topics.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4065,33 +4057,29 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" t="n">
+        <v>20</v>
+      </c>
+      <c r="D16" t="n">
         <v>16</v>
       </c>
-      <c r="C16" t="n">
-        <v>16</v>
-      </c>
-      <c r="D16" t="n">
-        <v>15</v>
-      </c>
       <c r="E16" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Below expectations — recommend extra classes after school.</t>
-        </is>
-      </c>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4100,24 +4088,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F17" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
@@ -4127,29 +4119,33 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>34</v>
+      </c>
+      <c r="C18" t="n">
+        <v>30</v>
+      </c>
+      <c r="D18" t="n">
+        <v>29</v>
+      </c>
+      <c r="E18" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" t="n">
         <v>33</v>
       </c>
-      <c r="C18" t="n">
-        <v>34</v>
-      </c>
-      <c r="D18" t="n">
-        <v>31</v>
-      </c>
-      <c r="E18" t="n">
-        <v>33</v>
-      </c>
-      <c r="F18" t="n">
-        <v>35</v>
-      </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>Reading Comprehension</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Great turnaround this term, keep the momentum going!</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4161,25 +4157,21 @@
         <v>29</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F19" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Reading Comprehension</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
@@ -4189,19 +4181,19 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C20" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D20" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F20" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -4211,7 +4203,11 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Solid understanding, encourage attempting harder problems.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4220,33 +4216,29 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="E21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F21" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4255,33 +4247,29 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C22" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E22" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Exceptional performance, keep up this standard.</t>
-        </is>
-      </c>
+          <t>The Ant and the Cricket (Poem)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4290,31 +4278,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" t="n">
+        <v>39</v>
+      </c>
+      <c r="D23" t="n">
         <v>43</v>
-      </c>
-      <c r="D23" t="n">
-        <v>42</v>
       </c>
       <c r="E23" t="n">
         <v>44</v>
       </c>
       <c r="F23" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Solid understanding, encourage attempting harder problems.</t>
+          <t>Strong performer, small gains possible with more practice.</t>
         </is>
       </c>
     </row>
@@ -4325,16 +4313,16 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>33</v>
+      </c>
+      <c r="C24" t="n">
+        <v>33</v>
+      </c>
+      <c r="D24" t="n">
+        <v>31</v>
+      </c>
+      <c r="E24" t="n">
         <v>30</v>
-      </c>
-      <c r="C24" t="n">
-        <v>35</v>
-      </c>
-      <c r="D24" t="n">
-        <v>32</v>
-      </c>
-      <c r="E24" t="n">
-        <v>35</v>
       </c>
       <c r="F24" t="n">
         <v>32</v>
@@ -4344,7 +4332,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Grammar - Tenses</t>
+          <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -4356,26 +4344,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D25" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E25" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F25" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Letter Writing</t>
+          <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -4387,19 +4375,19 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -4414,27 +4402,31 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
         <v>8</v>
-      </c>
-      <c r="C27" t="n">
-        <v>7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>7</v>
       </c>
       <c r="E27" t="n">
         <v>6</v>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Letter Writing</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -4445,29 +4437,29 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C28" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D28" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E28" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F28" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Great turnaround this term, keep the momentum going!</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Grammar - Tenses</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4476,26 +4468,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" t="n">
         <v>32</v>
-      </c>
-      <c r="D29" t="n">
-        <v>28</v>
       </c>
       <c r="E29" t="n">
         <v>32</v>
       </c>
       <c r="F29" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>The Ant and the Cricket (Poem)</t>
+          <t>Reading Comprehension</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4507,19 +4499,19 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>40</v>
+      </c>
+      <c r="C30" t="n">
+        <v>38</v>
+      </c>
+      <c r="D30" t="n">
         <v>41</v>
       </c>
-      <c r="C30" t="n">
-        <v>41</v>
-      </c>
-      <c r="D30" t="n">
-        <v>40</v>
-      </c>
       <c r="E30" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="F30" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -4534,26 +4526,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C31" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D31" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E31" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="F31" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Reading Comprehension</t>
+          <t>Letter Writing</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4637,26 +4629,26 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>100</v>
+      </c>
+      <c r="C2" t="n">
+        <v>92</v>
+      </c>
+      <c r="D2" t="n">
+        <v>96</v>
+      </c>
+      <c r="E2" t="n">
         <v>94</v>
       </c>
-      <c r="C2" t="n">
-        <v>88</v>
-      </c>
-      <c r="D2" t="n">
-        <v>92</v>
-      </c>
-      <c r="E2" t="n">
-        <v>86</v>
-      </c>
       <c r="F2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -4672,31 +4664,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C3" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D3" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="E3" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Doing very well overall, minor slips in application-based questions.</t>
+          <t>Solid understanding, encourage attempting harder problems.</t>
         </is>
       </c>
     </row>
@@ -4707,19 +4699,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C4" t="n">
         <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="E4" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F4" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -4731,7 +4723,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Steady but needs more consistency across topics.</t>
+          <t>On track, but should aim higher with focused practice.</t>
         </is>
       </c>
     </row>
@@ -4742,31 +4734,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C5" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" t="n">
         <v>61</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Gadya Pathya 1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4777,19 +4769,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C6" t="n">
+        <v>44</v>
+      </c>
+      <c r="D6" t="n">
+        <v>38</v>
+      </c>
+      <c r="E6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F6" t="n">
         <v>47</v>
-      </c>
-      <c r="D6" t="n">
-        <v>47</v>
-      </c>
-      <c r="E6" t="n">
-        <v>40</v>
-      </c>
-      <c r="F6" t="n">
-        <v>41</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -4812,27 +4804,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Needs urgent academic support, at risk of failing.</t>
+          <t>Very low scores across the board, please involve parents.</t>
         </is>
       </c>
     </row>
@@ -4843,27 +4839,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F8" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Encouraging progress, on the right track now.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -4874,19 +4874,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C9" t="n">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="D9" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F9" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -4898,7 +4898,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -4909,26 +4909,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C10" t="n">
+        <v>82</v>
+      </c>
+      <c r="D10" t="n">
+        <v>82</v>
+      </c>
+      <c r="E10" t="n">
+        <v>85</v>
+      </c>
+      <c r="F10" t="n">
         <v>83</v>
       </c>
-      <c r="D10" t="n">
-        <v>85</v>
-      </c>
-      <c r="E10" t="n">
-        <v>87</v>
-      </c>
-      <c r="F10" t="n">
-        <v>85</v>
-      </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4944,31 +4944,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D11" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E11" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Vyakarana Basics</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Inconsistent results — strong in some tests, weak in others.</t>
+          <t>Unpredictable performance, may help to identify what's different on good days.</t>
         </is>
       </c>
     </row>
@@ -4979,24 +4979,28 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>86</v>
+      </c>
+      <c r="C12" t="n">
+        <v>94</v>
+      </c>
+      <c r="D12" t="n">
+        <v>92</v>
+      </c>
+      <c r="E12" t="n">
         <v>89</v>
       </c>
-      <c r="C12" t="n">
-        <v>95</v>
-      </c>
-      <c r="D12" t="n">
-        <v>96</v>
-      </c>
-      <c r="E12" t="n">
-        <v>98</v>
-      </c>
       <c r="F12" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>Outstanding grasp of concepts, sets the benchmark for the class.</t>
@@ -5010,26 +5014,26 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="D13" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="E13" t="n">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="F13" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -5045,31 +5049,27 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D14" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="E14" t="n">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>On track, but should aim higher with focused practice.</t>
+          <t>Average performance — revision of basics recommended.</t>
         </is>
       </c>
     </row>
@@ -5080,19 +5080,19 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>50</v>
+      </c>
+      <c r="C15" t="n">
         <v>58</v>
-      </c>
-      <c r="C15" t="n">
-        <v>51</v>
       </c>
       <c r="D15" t="n">
         <v>57</v>
       </c>
       <c r="E15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F15" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -5111,19 +5111,19 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F16" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -5135,7 +5135,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Below expectations — recommend extra classes after school.</t>
+          <t>Finding it difficult to keep pace, needs individual attention.</t>
         </is>
       </c>
     </row>
@@ -5146,19 +5146,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E17" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -5181,28 +5181,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C18" t="n">
+        <v>80</v>
+      </c>
+      <c r="D18" t="n">
+        <v>87</v>
+      </c>
+      <c r="E18" t="n">
         <v>83</v>
       </c>
-      <c r="D18" t="n">
-        <v>79</v>
-      </c>
-      <c r="E18" t="n">
-        <v>75</v>
-      </c>
       <c r="F18" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Padya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -5216,24 +5212,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E19" t="n">
         <v>56</v>
       </c>
       <c r="F19" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Gadya Pathya 1</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5250,21 +5250,25 @@
         <v>85</v>
       </c>
       <c r="C20" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D20" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F20" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Vyakarana Basics</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -5278,19 +5282,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="C21" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F21" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -5313,26 +5317,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C22" t="n">
         <v>91</v>
       </c>
       <c r="D22" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="E22" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -5348,28 +5352,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="C23" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D23" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E23" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F23" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -5383,19 +5383,19 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C24" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D24" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E24" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -5418,26 +5418,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="C25" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D25" t="n">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E25" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F25" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Padya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -5453,16 +5453,16 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C26" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D26" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="E26" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F26" t="n">
         <v>38</v>
@@ -5473,7 +5473,7 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Struggling with fundamentals, needs remedial sessions.</t>
+          <t>Below expectations — recommend extra classes after school.</t>
         </is>
       </c>
     </row>
@@ -5484,22 +5484,22 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14</v>
+      </c>
+      <c r="E27" t="n">
         <v>13</v>
       </c>
-      <c r="C27" t="n">
-        <v>15</v>
-      </c>
-      <c r="D27" t="n">
-        <v>17</v>
-      </c>
-      <c r="E27" t="n">
-        <v>17</v>
-      </c>
       <c r="F27" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -5519,31 +5519,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C28" t="n">
-        <v>72</v>
+        <v>86</v>
       </c>
       <c r="D28" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E28" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="F28" t="n">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Padya Pathya 1</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Visible improvement — the extra effort is showing results.</t>
+          <t>Great turnaround this term, keep the momentum going!</t>
         </is>
       </c>
     </row>
@@ -5554,27 +5554,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C29" t="n">
+        <v>61</v>
+      </c>
+      <c r="D29" t="n">
+        <v>57</v>
+      </c>
+      <c r="E29" t="n">
         <v>64</v>
       </c>
-      <c r="D29" t="n">
-        <v>61</v>
-      </c>
-      <c r="E29" t="n">
-        <v>62</v>
-      </c>
       <c r="F29" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Padya Pathya 1</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Average performance — revision of basics recommended.</t>
+          <t>Steady but needs more consistency across topics.</t>
         </is>
       </c>
     </row>
@@ -5585,31 +5589,27 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="C30" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D30" t="n">
+        <v>86</v>
+      </c>
+      <c r="E30" t="n">
         <v>79</v>
       </c>
-      <c r="E30" t="n">
-        <v>80</v>
-      </c>
       <c r="F30" t="n">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Gadya Pathya 1</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Strong performer, small gains possible with more practice.</t>
+          <t>Doing very well overall, minor slips in application-based questions.</t>
         </is>
       </c>
     </row>
@@ -5620,26 +5620,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C31" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="E31" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F31" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Gadya Pathya 1</t>
+          <t>Vyakarana Basics</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">

--- a/samples/Sample_7_For_School_Management_Section_A_Class7.xlsx
+++ b/samples/Sample_7_For_School_Management_Section_A_Class7.xlsx
@@ -9,10 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SETUP" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="STUDENTS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Final Exam" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Unit Test 1" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Mid-Term" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Unit Test 2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Class7A-Final Exam" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -637,7 +637,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unit Test 1</t>
+          <t>Class7A-Unit Test 1</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Mid-Term</t>
+          <t>Class7A-Mid-Term</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Unit Test 2</t>
+          <t>Class7A-Unit Test 2</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Final Exam</t>
+          <t>Class7A-Final Exam</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1668,7 +1667,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1729,8 +1727,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1831,7 +1827,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1857,7 +1852,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -1893,7 +1887,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1924,7 +1917,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1955,7 +1947,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1986,7 +1977,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2082,7 +2072,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Finding it difficult to keep pace, needs individual attention.</t>
@@ -2113,8 +2102,6 @@
       <c r="G17" t="n">
         <v>0</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2145,7 +2132,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2246,7 +2232,6 @@
           <t>Ratio &amp; Proportion</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2277,7 +2262,6 @@
           <t>Simple Equations</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2308,7 +2292,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2334,7 +2317,6 @@
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>On track, but should aim higher with focused practice.</t>
@@ -2365,8 +2347,6 @@
       <c r="G25" t="n">
         <v>0</v>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2392,8 +2372,6 @@
       <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2494,7 +2472,6 @@
           <t>Perimeter &amp; Area</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2525,7 +2502,6 @@
           <t>Fractions &amp; Decimals</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2556,7 +2532,6 @@
           <t>Lines &amp; Angles</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2654,8 +2629,6 @@
       <c r="G2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2686,7 +2659,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2717,7 +2689,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2743,8 +2714,6 @@
       <c r="G5" t="n">
         <v>0</v>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2775,7 +2744,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2806,7 +2774,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2837,7 +2804,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2868,7 +2834,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2894,7 +2859,6 @@
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -2925,8 +2889,6 @@
       <c r="G11" t="n">
         <v>0</v>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2957,7 +2919,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2983,8 +2944,6 @@
       <c r="G13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3015,7 +2974,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3041,8 +2999,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3068,8 +3024,6 @@
       <c r="G16" t="n">
         <v>0</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3100,7 +3054,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3131,7 +3084,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3157,8 +3109,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3189,7 +3139,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3215,8 +3164,6 @@
       <c r="G21" t="n">
         <v>0</v>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3247,7 +3194,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3348,7 +3294,6 @@
           <t>Motion &amp; Time</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3379,7 +3324,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3405,8 +3349,6 @@
       <c r="G27" t="n">
         <v>0</v>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3437,7 +3379,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3468,7 +3409,6 @@
           <t>Acids Bases &amp; Salts</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3499,7 +3439,6 @@
           <t>Nutrition in Plants</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3530,7 +3469,6 @@
           <t>Weather &amp; Climate</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3633,7 +3571,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -3664,7 +3601,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3695,7 +3631,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3761,7 +3696,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3827,7 +3761,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3853,7 +3786,6 @@
       <c r="G9" t="n">
         <v>0</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Steady but needs more consistency across topics.</t>
@@ -3889,7 +3821,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3920,7 +3851,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3951,7 +3881,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3982,7 +3911,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4013,7 +3941,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4079,7 +4006,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4110,7 +4036,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4171,8 +4096,6 @@
       <c r="G19" t="n">
         <v>0</v>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4238,7 +4161,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4269,7 +4191,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4335,7 +4256,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4366,7 +4286,6 @@
           <t>The Ant and the Cricket (Poem)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4392,8 +4311,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4459,7 +4376,6 @@
           <t>Grammar - Tenses</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4490,7 +4406,6 @@
           <t>Reading Comprehension</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4516,8 +4431,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4548,7 +4461,6 @@
           <t>Letter Writing</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5066,7 +4978,6 @@
       <c r="G14" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5097,7 +5008,6 @@
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Average performance — revision of basics recommended.</t>
@@ -5198,7 +5108,6 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Great turnaround this term, keep the momentum going!</t>
@@ -5369,7 +5278,6 @@
       <c r="G23" t="n">
         <v>0</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
@@ -5470,7 +5378,6 @@
       <c r="G26" t="n">
         <v>0</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Below expectations — recommend extra classes after school.</t>
@@ -5606,7 +5513,6 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Doing very well overall, minor slips in application-based questions.</t>
